--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -494,7 +494,7 @@
         <v>31.18</v>
       </c>
       <c r="L3">
-        <v>2.104208711401695</v>
+        <v>2.1042087114017</v>
       </c>
     </row>
     <row r="4">
@@ -532,7 +532,7 @@
         <v>45</v>
       </c>
       <c r="L4">
-        <v>2.115328960348016</v>
+        <v>2.11532896034802</v>
       </c>
     </row>
     <row r="5">
@@ -603,6 +603,12 @@
       </c>
       <c r="J6">
         <v>50</v>
+      </c>
+      <c r="K6">
+        <v>43.11</v>
+      </c>
+      <c r="L6">
+        <v>1.408718840900953</v>
       </c>
     </row>
     <row r="7">

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -642,6 +642,12 @@
       <c r="J7">
         <v>50</v>
       </c>
+      <c r="K7">
+        <v>1.94</v>
+      </c>
+      <c r="L7">
+        <v>1.125237801862997</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -680,6 +680,12 @@
       <c r="J8">
         <v>50</v>
       </c>
+      <c r="K8">
+        <v>45</v>
+      </c>
+      <c r="L8">
+        <v>4.29188845066153</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -718,6 +718,12 @@
       <c r="J9">
         <v>50</v>
       </c>
+      <c r="K9">
+        <v>11.41</v>
+      </c>
+      <c r="L9">
+        <v>2.675639763086159</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -750,6 +756,12 @@
       <c r="J10">
         <v>50</v>
       </c>
+      <c r="K10">
+        <v>45</v>
+      </c>
+      <c r="L10">
+        <v>2.911811129785847</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -781,6 +793,12 @@
       </c>
       <c r="J11">
         <v>50</v>
+      </c>
+      <c r="K11">
+        <v>41.82</v>
+      </c>
+      <c r="L11">
+        <v>0.946895983206014</v>
       </c>
     </row>
     <row r="12">
@@ -814,6 +832,12 @@
       <c r="J12">
         <v>50</v>
       </c>
+      <c r="K12">
+        <v>45</v>
+      </c>
+      <c r="L12">
+        <v>0.4363781816036579</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -846,6 +870,12 @@
       <c r="J13">
         <v>50</v>
       </c>
+      <c r="K13">
+        <v>28.12</v>
+      </c>
+      <c r="L13">
+        <v>1.062147401564931</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -877,6 +907,12 @@
       </c>
       <c r="J14">
         <v>50</v>
+      </c>
+      <c r="K14">
+        <v>45</v>
+      </c>
+      <c r="L14">
+        <v>6.243920301768861</v>
       </c>
     </row>
     <row r="15">

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -946,6 +946,12 @@
       <c r="J15">
         <v>50</v>
       </c>
+      <c r="K15">
+        <v>45</v>
+      </c>
+      <c r="L15">
+        <v>4.393798768139085</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -978,6 +984,12 @@
       <c r="J16">
         <v>50</v>
       </c>
+      <c r="K16">
+        <v>45</v>
+      </c>
+      <c r="L16">
+        <v>3.427596519565759</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1009,6 +1021,12 @@
       </c>
       <c r="J17">
         <v>50</v>
+      </c>
+      <c r="K17">
+        <v>45</v>
+      </c>
+      <c r="L17">
+        <v>4.221823716290046</v>
       </c>
     </row>
     <row r="18">
@@ -1041,6 +1059,12 @@
       </c>
       <c r="J18">
         <v>50</v>
+      </c>
+      <c r="K18">
+        <v>28.17</v>
+      </c>
+      <c r="L18">
+        <v>2.093168037678033</v>
       </c>
     </row>
     <row r="19">

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -1098,6 +1098,12 @@
       <c r="J19">
         <v>50</v>
       </c>
+      <c r="K19">
+        <v>10.07</v>
+      </c>
+      <c r="L19">
+        <v>1.113057437175216</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1129,6 +1135,12 @@
       </c>
       <c r="J20">
         <v>50</v>
+      </c>
+      <c r="K20">
+        <v>45</v>
+      </c>
+      <c r="L20">
+        <v>4.221823716290046</v>
       </c>
     </row>
     <row r="21">

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -1174,6 +1174,12 @@
       <c r="J21">
         <v>50</v>
       </c>
+      <c r="K21">
+        <v>45</v>
+      </c>
+      <c r="L21">
+        <v>1.289884803763549</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1206,6 +1212,12 @@
       <c r="J22">
         <v>50</v>
       </c>
+      <c r="K22">
+        <v>26.79</v>
+      </c>
+      <c r="L22">
+        <v>1.084525944040509</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1237,6 +1249,12 @@
       </c>
       <c r="J23">
         <v>50</v>
+      </c>
+      <c r="K23">
+        <v>45</v>
+      </c>
+      <c r="L23">
+        <v>4.221823716290046</v>
       </c>
     </row>
     <row r="24">
@@ -1270,6 +1288,12 @@
       <c r="J24">
         <v>50</v>
       </c>
+      <c r="K24">
+        <v>21.75</v>
+      </c>
+      <c r="L24">
+        <v>2.169901627567868</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1301,6 +1325,12 @@
       </c>
       <c r="J25">
         <v>50</v>
+      </c>
+      <c r="K25">
+        <v>45</v>
+      </c>
+      <c r="L25">
+        <v>2.744709327553498</v>
       </c>
     </row>
     <row r="26">
@@ -1366,6 +1396,12 @@
       <c r="J27">
         <v>50</v>
       </c>
+      <c r="K27">
+        <v>45</v>
+      </c>
+      <c r="L27">
+        <v>0.4343582783390509</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1397,6 +1433,12 @@
       </c>
       <c r="J28">
         <v>50</v>
+      </c>
+      <c r="K28">
+        <v>28.17</v>
+      </c>
+      <c r="L28">
+        <v>1.046584018839016</v>
       </c>
     </row>
     <row r="29">

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -10,9 +10,6 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$N$52</definedName>
-  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -23,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
   <si>
     <t xml:space="preserve">tau</t>
   </si>
@@ -187,10 +184,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -198,11 +191,8 @@
   </sheetPr>
   <dimension ref="A1:N52"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12.68"/>
-  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1457,6 +1447,15 @@
       <c r="J31" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K31" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L31" s="0" t="n">
+        <v>3.46800637204895</v>
+      </c>
+      <c r="N31" s="0" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="n">
@@ -1488,6 +1487,15 @@
       </c>
       <c r="J32" s="0" t="n">
         <v>50</v>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L32" s="0" t="n">
+        <v>4.22180666415151</v>
+      </c>
+      <c r="N32" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1521,6 +1529,15 @@
       <c r="J33" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K33" s="0" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="L33" s="0" t="n">
+        <v>2.09293119422977</v>
+      </c>
+      <c r="N33" s="0" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="n">
@@ -1553,6 +1570,15 @@
       <c r="J34" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K34" s="0" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="L34" s="0" t="n">
+        <v>1.05904452595794</v>
+      </c>
+      <c r="N34" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="n">
@@ -1584,6 +1610,15 @@
       </c>
       <c r="J35" s="0" t="n">
         <v>50</v>
+      </c>
+      <c r="K35" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L35" s="0" t="n">
+        <v>4.22180666415151</v>
+      </c>
+      <c r="N35" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2131,7 +2166,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N52"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2139,6 +2173,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="21">
   <si>
     <t xml:space="preserve">tau</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
   </si>
 </sst>
 </file>
@@ -1251,6 +1254,12 @@
       <c r="J26" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K26" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" s="0" t="n">
+        <v>4.0134806885418</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="n">
@@ -1652,6 +1661,15 @@
       <c r="J36" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K36" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L36" s="0" t="n">
+        <v>1.28986015831199</v>
+      </c>
+      <c r="N36" s="0" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="n">
@@ -1684,6 +1702,15 @@
       <c r="J37" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K37" s="0" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="L37" s="0" t="n">
+        <v>1.08423973704942</v>
+      </c>
+      <c r="N37" s="0" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="n">
@@ -1715,6 +1742,15 @@
       </c>
       <c r="J38" s="0" t="n">
         <v>50</v>
+      </c>
+      <c r="K38" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L38" s="0" t="n">
+        <v>4.22180666415151</v>
+      </c>
+      <c r="N38" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2004,6 +2040,15 @@
       <c r="J47" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K47" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L47" s="0" t="n">
+        <v>4.22495799083875</v>
+      </c>
+      <c r="M47" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="n">
@@ -2036,6 +2081,15 @@
       <c r="J48" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K48" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L48" s="0" t="n">
+        <v>4.22495799083875</v>
+      </c>
+      <c r="M48" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="n">
@@ -2068,6 +2122,15 @@
       <c r="J49" s="0" t="n">
         <v>100</v>
       </c>
+      <c r="K49" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L49" s="0" t="n">
+        <v>4.40433382613399</v>
+      </c>
+      <c r="M49" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="n">
@@ -2100,6 +2163,15 @@
       <c r="J50" s="0" t="n">
         <v>100</v>
       </c>
+      <c r="K50" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L50" s="0" t="n">
+        <v>8.40433382613399</v>
+      </c>
+      <c r="M50" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="n">
@@ -2132,6 +2204,15 @@
       <c r="J51" s="0" t="n">
         <v>500</v>
       </c>
+      <c r="K51" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L51" s="0" t="n">
+        <v>18.02166913067</v>
+      </c>
+      <c r="M51" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="n">
@@ -2163,6 +2244,15 @@
       </c>
       <c r="J52" s="0" t="n">
         <v>500</v>
+      </c>
+      <c r="K52" s="0" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="L52" s="0" t="n">
+        <v>9.83130940628982</v>
+      </c>
+      <c r="M52" s="0" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="21">
   <si>
     <t xml:space="preserve">tau</t>
   </si>
@@ -192,7 +192,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1944,6 +1944,15 @@
       <c r="J44" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K44" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L44" s="0" t="n">
+        <v>6.24180122162956</v>
+      </c>
+      <c r="N44" s="0" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="n">
@@ -2008,8 +2017,17 @@
       <c r="J46" s="0" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K46" s="0" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="L46" s="0" t="n">
+        <v>3.54014716892888</v>
+      </c>
+      <c r="N46" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="n">
         <v>1</v>
       </c>
@@ -2046,11 +2064,11 @@
       <c r="L47" s="0" t="n">
         <v>4.22495799083875</v>
       </c>
-      <c r="M47" s="0" t="s">
+      <c r="N47" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="n">
         <v>1</v>
       </c>
@@ -2087,11 +2105,11 @@
       <c r="L48" s="0" t="n">
         <v>4.22495799083875</v>
       </c>
-      <c r="M48" s="0" t="s">
+      <c r="N48" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="n">
         <v>1</v>
       </c>
@@ -2128,11 +2146,11 @@
       <c r="L49" s="0" t="n">
         <v>4.40433382613399</v>
       </c>
-      <c r="M49" s="0" t="s">
+      <c r="N49" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="n">
         <v>1</v>
       </c>
@@ -2169,11 +2187,11 @@
       <c r="L50" s="0" t="n">
         <v>8.40433382613399</v>
       </c>
-      <c r="M50" s="0" t="s">
+      <c r="N50" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="n">
         <v>1</v>
       </c>
@@ -2210,11 +2228,11 @@
       <c r="L51" s="0" t="n">
         <v>18.02166913067</v>
       </c>
-      <c r="M51" s="0" t="s">
+      <c r="N51" s="0" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="n">
         <v>1</v>
       </c>
@@ -2251,8 +2269,84 @@
       <c r="L52" s="0" t="n">
         <v>9.83130940628982</v>
       </c>
-      <c r="M52" s="0" t="s">
+      <c r="N52" s="0" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="K53" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="L53" s="0" t="n">
+        <v>18.02166913067</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F54" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J54" s="0" t="n">
+        <v>500</v>
+      </c>
+      <c r="K54" s="0" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="L54" s="0" t="n">
+        <v>9.83130940628982</v>
       </c>
     </row>
   </sheetData>

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -461,7 +461,7 @@
         <v>45</v>
       </c>
       <c r="L2">
-        <v>4.450856615123254</v>
+        <v>4.45085661512325</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         <v>32.5</v>
       </c>
       <c r="L3">
-        <v>2.083702888375848</v>
+        <v>2.08370288837585</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>45</v>
       </c>
       <c r="L4">
-        <v>2.145170551124968</v>
+        <v>2.14517055112497</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         <v>45</v>
       </c>
       <c r="L5">
-        <v>4.450856615123254</v>
+        <v>4.45085661512325</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>45</v>
       </c>
       <c r="L7">
-        <v>1.086776212624662</v>
+        <v>1.08677621262466</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>45</v>
       </c>
       <c r="L8">
-        <v>4.450856615123254</v>
+        <v>4.45085661512325</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
       <c r="L9">
-        <v>2.676328091146634</v>
+        <v>2.67632809114663</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>45</v>
       </c>
       <c r="L10">
-        <v>2.925012341872171</v>
+        <v>2.92501234187217</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>43</v>
       </c>
       <c r="L11">
-        <v>0.4622615039770768</v>
+        <v>0.462261503977077</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>32.5</v>
       </c>
       <c r="L13">
-        <v>1.041851444187924</v>
+        <v>1.04185144418792</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>43</v>
       </c>
       <c r="L14">
-        <v>6.666280724870201</v>
+        <v>6.6662807248702</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="L15">
-        <v>4.290341102249935</v>
+        <v>4.29034110224994</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>45</v>
       </c>
       <c r="L16">
-        <v>3.467234818528875</v>
+        <v>3.46723481852888</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="L17">
-        <v>4.450684443115732</v>
+        <v>4.45068444311573</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>32.5</v>
       </c>
       <c r="L18">
-        <v>2.071223794332217</v>
+        <v>2.07122379433222</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>3.5</v>
       </c>
       <c r="L19">
-        <v>1.134716957341744</v>
+        <v>1.13471695734174</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45</v>
       </c>
       <c r="L20">
-        <v>4.450684443115732</v>
+        <v>4.45068444311573</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>41</v>
       </c>
       <c r="L21">
-        <v>1.347917764978871</v>
+        <v>1.34791776497887</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>45</v>
       </c>
       <c r="L22">
-        <v>1.062661317432913</v>
+        <v>1.06266131743291</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>45</v>
       </c>
       <c r="L23">
-        <v>4.450684443115732</v>
+        <v>4.45068444311573</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>12</v>
       </c>
       <c r="L24">
-        <v>2.191190396458613</v>
+        <v>2.19119039645861</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>45</v>
       </c>
       <c r="L25">
-        <v>2.917425622542154</v>
+        <v>2.91742562254215</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>45</v>
       </c>
       <c r="L27">
-        <v>0.5703283109661823</v>
+        <v>0.570328310966182</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>32.5</v>
       </c>
       <c r="L28">
-        <v>1.035611897166109</v>
+        <v>1.03561189716611</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>3.5</v>
       </c>
       <c r="L30">
-        <v>2.269433914683488</v>
+        <v>2.26943391468349</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45</v>
       </c>
       <c r="L31">
-        <v>3.607211666993096</v>
+        <v>3.6072116669931</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45</v>
       </c>
       <c r="L32">
-        <v>4.450684442934887</v>
+        <v>4.45068444293489</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>32.5</v>
       </c>
       <c r="L33">
-        <v>2.071157793691812</v>
+        <v>2.07115779369181</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>7</v>
       </c>
       <c r="L34">
-        <v>1.097029874209964</v>
+        <v>1.09702987420996</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>45</v>
       </c>
       <c r="L35">
-        <v>4.450684442934887</v>
+        <v>4.45068444293489</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>41</v>
       </c>
       <c r="L36">
-        <v>1.347917509105698</v>
+        <v>1.3479175091057</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>45</v>
       </c>
       <c r="L37">
-        <v>1.062660313375855</v>
+        <v>1.06266031337586</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45</v>
       </c>
       <c r="L38">
-        <v>4.450684442934887</v>
+        <v>4.45068444293489</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2043,6 +2043,12 @@
       <c r="J39">
         <v>50</v>
       </c>
+      <c r="K39">
+        <v>15</v>
+      </c>
+      <c r="L39">
+        <v>2.189077109839192</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -2075,6 +2081,12 @@
       <c r="J40">
         <v>50</v>
       </c>
+      <c r="K40">
+        <v>7.5</v>
+      </c>
+      <c r="L40">
+        <v>1.519362984152868</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -2106,6 +2118,12 @@
       </c>
       <c r="J41">
         <v>50</v>
+      </c>
+      <c r="K41">
+        <v>43</v>
+      </c>
+      <c r="L41">
+        <v>0.4622612726611661</v>
       </c>
     </row>
     <row r="42">
@@ -2139,6 +2157,12 @@
       <c r="J42">
         <v>50</v>
       </c>
+      <c r="K42">
+        <v>45</v>
+      </c>
+      <c r="L42">
+        <v>0.5703283098636078</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -2171,6 +2195,12 @@
       <c r="J43">
         <v>50</v>
       </c>
+      <c r="K43">
+        <v>32.5</v>
+      </c>
+      <c r="L43">
+        <v>1.035578896845906</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -2207,7 +2237,7 @@
         <v>43</v>
       </c>
       <c r="L44">
-        <v>6.664160816390678</v>
+        <v>6.66416081639068</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -2282,7 +2312,7 @@
         <v>7.5</v>
       </c>
       <c r="L46">
-        <v>3.559135447802053</v>
+        <v>3.55913544780205</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -2325,7 +2355,7 @@
         <v>45</v>
       </c>
       <c r="L47">
-        <v>4.450856615123254</v>
+        <v>4.45085661512325</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -2368,7 +2398,7 @@
         <v>45</v>
       </c>
       <c r="L48">
-        <v>4.450856615123254</v>
+        <v>4.45085661512325</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -2411,7 +2441,7 @@
         <v>44</v>
       </c>
       <c r="L49">
-        <v>4.655860400222284</v>
+        <v>4.65586040022228</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -2454,7 +2484,7 @@
         <v>44</v>
       </c>
       <c r="L50">
-        <v>8.655860400222286</v>
+        <v>8.65586040022229</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -2497,7 +2527,7 @@
         <v>44</v>
       </c>
       <c r="L51">
-        <v>19.27930200111143</v>
+        <v>19.2793020011114</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -2540,7 +2570,7 @@
         <v>42</v>
       </c>
       <c r="L52">
-        <v>8.795536059617058</v>
+        <v>8.79553605961706</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -2582,9 +2612,6 @@
       <c r="K53">
         <v>45</v>
       </c>
-      <c r="L53">
-        <v>18.02166913067</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -2619,9 +2646,6 @@
       </c>
       <c r="K54">
         <v>43.97</v>
-      </c>
-      <c r="L54">
-        <v>9.831309406289821</v>
       </c>
     </row>
   </sheetData>

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="22">
   <si>
     <t xml:space="preserve">tau</t>
   </si>
@@ -1797,7 +1797,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="n">
         <v>10</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="n">
         <v>5</v>
       </c>
@@ -2033,6 +2033,15 @@
       <c r="J45" s="0" t="n">
         <v>50</v>
       </c>
+      <c r="K45" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="L45" s="0" t="n">
+        <v>2.19405974841993</v>
+      </c>
+      <c r="N45" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="n">
@@ -2388,7 +2397,13 @@
         <v>500</v>
       </c>
       <c r="K54" s="0" t="n">
-        <v>43.97</v>
+        <v>42</v>
+      </c>
+      <c r="L54" s="0" t="n">
+        <v>8.79553605961706</v>
+      </c>
+      <c r="N54" s="0" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -196,7 +196,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N54"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/Figures2/res.xlsx
+++ b/Figures2/res.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t xml:space="preserve">tau</t>
   </si>
@@ -196,7 +196,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N54"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1258,10 +1258,13 @@
         <v>50</v>
       </c>
       <c r="K26" s="0" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="L26" s="0" t="n">
-        <v>4.0134806885418</v>
+        <v>0.462261272661442</v>
+      </c>
+      <c r="N26" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2362,7 +2365,13 @@
         <v>500</v>
       </c>
       <c r="K53" s="0" t="n">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="L53" s="0" t="n">
+        <v>19.2780331349144</v>
+      </c>
+      <c r="N53" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2400,7 +2409,7 @@
         <v>42</v>
       </c>
       <c r="L54" s="0" t="n">
-        <v>8.79553605961706</v>
+        <v>8.79504127262569</v>
       </c>
       <c r="N54" s="0" t="s">
         <v>21</v>
